--- a/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionLaboratorySecondIntentionResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:19:44+00:00</t>
+    <t>2026-09-14T09:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
